--- a/marketing/plan-marketing-auditorias-en-linea.xlsx
+++ b/marketing/plan-marketing-auditorias-en-linea.xlsx
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
@@ -1304,30 +1304,32 @@
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>¿Tu SGI vive en 40 planillas de Excel?</t>
+          <t>No necesitás 21 módulos para hacer una auditoría</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr">
         <is>
-          <t>¿Tu Sistema de Gestión está repartido en decenas de Excel y carpetas que nadie encuentra el día de la auditoría? 😰
-Calidad por un lado, ambiente por otro, seguridad en papel… y la evidencia, perdida.
-Hay una forma más simple: UNA plataforma donde ISO 9001, 14001 y 45001 conviven, con todo trazable y a mano.
-Así trabajás con Auditorías en Línea.</t>
+          <t>Abrís el sistema de gestión y te encontrás con veintidós secciones en el menú. Huella de carbono, revisión por la dirección, mantenimiento… todas vacías.
+El tamaño no es gratis: cada módulo que no usás es una decisión más que tomar antes de hacer lo que viniste a hacer.
+Ahora elegís el alcance al crear la cuenta:
+▸ Auditorías — cinco secciones, para ejecutar auditorías internas en cualquier industria.
+▸ SGI Completo — todo, del diagnóstico a la revisión por la dirección.
+Y no es una decisión definitiva: pasás de una a la otra cuando quieras. Lo que se enciende o se apaga es el acceso a las secciones, nunca la información cargada.</t>
         </is>
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>#ISO9001 #ISO14001 #ISO45001 #SistemasDeGestión #Calidad #Excel #MejoraContinua</t>
+          <t>#AuditoríasEnLínea #SGI #ISO9001 #ISO45001 #AuditoríaInterna #Mendoza</t>
         </is>
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>Pedí tu demo gratis 👉 auditoriasenlinea.com.ar</t>
+          <t>¿Con cuánta plataforma querés empezar? → auditoriasenlinea.com.ar</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr">
         <is>
-          <t>Carrusel comparativo: 'Antes (Excel/papel)' vs 'Después (plataforma)'.</t>
+          <t>Carrusel: slide 1 menú largo agobiante / slide 2 la pregunta del asistente / slide 3 menú corto de cinco secciones / slide 4 las dos ediciones comparadas.</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1339,7 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
@@ -1395,7 +1397,7 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -1454,7 +1456,7 @@
       </c>
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C7" s="37" t="inlineStr">
@@ -1469,40 +1471,40 @@
       </c>
       <c r="E7" s="39" t="inlineStr">
         <is>
-          <t>Dato / Beneficio</t>
+          <t>Consultor / Partner</t>
         </is>
       </c>
       <c r="F7" s="38" t="inlineStr">
         <is>
-          <t>Imagen</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="G7" s="40" t="inlineStr">
         <is>
-          <t>El tiempo se va buscando evidencia</t>
+          <t>Si auditás para otros, tus clientes van en tu cartera</t>
         </is>
       </c>
       <c r="H7" s="38" t="inlineStr">
         <is>
-          <t>En muchas organizaciones, buena parte del tiempo de una auditoría se pierde en una sola cosa: BUSCAR la evidencia. 🔍
-Procedimientos, registros, certificados de calibración… cada uno en un lugar distinto.
-Con un repositorio documental central y versionado, la evidencia aparece en segundos. El auditor pregunta, vos mostrás.
-[Dato: reemplazá por tu propia métrica de tiempo ahorrado]</t>
+          <t>Durante años los sistemas de gestión asumieron lo mismo: que la empresa audita su propia casa.
+Para un consultor con quince clientes eso significa que cada auditoría sale con el nombre y el domicilio de su propio estudio. Y que su auditor llega a la puerta equivocada.
+Cargás cada empresa auditada una vez —domicilio, actividad, identificación y referente en sitio— y de ahí en más cada visita sale con los datos del cliente. Con el pin del mapa, para llegar y no dar vueltas.
+¿Dejaste de trabajar con uno? Lo desactivás: sale del selector y su historial de auditorías queda intacto.</t>
         </is>
       </c>
       <c r="I7" s="38" t="inlineStr">
         <is>
-          <t>#ISO9001 #ISO14001 #ISO45001 #SistemasDeGestión #Calidad #GestiónDocumental #Auditorías</t>
+          <t>#AuditoríasEnLínea #AuditorLíder #Consultoría #ISO9001 #AuditoríaInterna #Mendoza</t>
         </is>
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>Contanos en los comentarios 👇</t>
+          <t>Si auditás para otros, esto es para vos → auditoriasenlinea.com.ar</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>Imagen: reloj + carpetas ordenadas vs papeles volando.</t>
+          <t>Carrusel: slide 1 auditor perdido frente a una puerta cerrada / slide 2 ficha de la empresa auditada / slide 3 la asignación completándose sola / slide 4 el pin en el mapa del celular.</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1514,7 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -1572,7 +1574,7 @@
       </c>
       <c r="B9" s="42" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="C9" s="42" t="inlineStr">
@@ -1629,7 +1631,7 @@
       </c>
       <c r="B10" s="42" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="C10" s="42" t="inlineStr">
@@ -1687,7 +1689,7 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -1747,7 +1749,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -1807,7 +1809,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -1865,7 +1867,7 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
@@ -1880,40 +1882,39 @@
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
-          <t>Dato / Beneficio</t>
+          <t>Consultor / Partner</t>
         </is>
       </c>
       <c r="F14" s="38" t="inlineStr">
         <is>
-          <t>Imagen</t>
+          <t>Imagen + texto</t>
         </is>
       </c>
       <c r="G14" s="40" t="inlineStr">
         <is>
-          <t>Menos papel = menos costo (y menos riesgo)</t>
+          <t>Tu checklist de Excel ya es una plantilla</t>
         </is>
       </c>
       <c r="H14" s="38" t="inlineStr">
         <is>
-          <t>El papel no solo cuesta impresión y espacio. Cuesta TIEMPO: copiar, archivar, transcribir, buscar. Y cada transcripción suma errores.
-Digitalizar tu SGI reduce ese costo oculto y baja el riesgo de perder evidencia.
-🌱 Bonus: menos papel también es un aporte a tu ISO 14001.
-[Dato: sumá tu propio ahorro estimado]</t>
+          <t>Una bodega, una obra y una clínica no se auditan con la misma hoja. Por eso no te obligamos a usar un checklist ISO.
+Importás el tuyo desde Excel o CSV y lo ves en pantalla antes de guardar nada. El importador reconoce el separador solo —sí, también el punto y coma del Excel en español—, acepta sinónimos de columna con o sin tildes, y si dos filas vienen mal armadas importa las otras noventa y ocho y te dice cuáles fallaron, por número de fila.
+Porque rechazar cien filas por dos malas te obliga a adivinar cuáles son.</t>
         </is>
       </c>
       <c r="I14" s="38" t="inlineStr">
         <is>
-          <t>#ISO9001 #ISO14001 #ISO45001 #SistemasDeGestión #Calidad #MedioAmbiente #Eficiencia #ISO14001</t>
+          <t>#AuditoríasEnLínea #AuditorLíder #Consultoría #ISO9001 #AuditoríaInterna #Mendoza</t>
         </is>
       </c>
       <c r="J14" s="38" t="inlineStr">
         <is>
-          <t>Conocé la plataforma 👉 auditoriasenlinea.com.ar</t>
+          <t>Traé tu checklist → auditoriasenlinea.com.ar</t>
         </is>
       </c>
       <c r="K14" s="38" t="inlineStr">
         <is>
-          <t>Infografía: costos ocultos del papel.</t>
+          <t>Planilla de Excel a la izquierda, vista previa de la plantilla importada a la derecha, flecha en el medio.</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1924,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -1980,7 +1981,7 @@
       </c>
       <c r="B16" s="42" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="C16" s="42" t="inlineStr">
@@ -2005,33 +2006,32 @@
       </c>
       <c r="G16" s="45" t="inlineStr">
         <is>
-          <t>Encuesta: ¿dónde vive hoy tu SGI?</t>
+          <t>Encuesta: ¿viniste a auditar o a implementar?</t>
         </is>
       </c>
       <c r="H16" s="43" t="inlineStr">
         <is>
-          <t>Sinceramente… ¿dónde vive hoy tu Sistema de Gestión? 🤔
-Votá 👇
-📊 Excel y carpetas compartidas
-📁 Papel + biblioratos
-💻 Un software de gestión
-🤯 Un poco de todo
-Spoiler: la mayoría marca la última. Y está perfecto reconocerlo: es el primer paso para ordenarlo.</t>
+          <t>Es la única pregunta que hacemos al crear una cuenta, y define cuánta plataforma ves.
+Nos da curiosidad cómo se reparte acá. ¿Qué estás haciendo hoy?
+▸ Ejecuto auditorías internas
+▸ Estoy implementando un SGI
+▸ Las dos cosas
+▸ Todavía lo llevo en Excel</t>
         </is>
       </c>
       <c r="I16" s="43" t="inlineStr">
         <is>
-          <t>#ISO9001 #ISO14001 #ISO45001 #SistemasDeGestión #Calidad #SGI #Calidad</t>
+          <t>#AuditoríasEnLínea #SGI #ISO9001 #AuditoríaInterna #Encuesta</t>
         </is>
       </c>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Contanos en los comentarios 👇</t>
+          <t>Contestá en la encuesta 👇</t>
         </is>
       </c>
       <c r="K16" s="43" t="inlineStr">
         <is>
-          <t>Encuesta nativa de LinkedIn/IG (sticker de pregunta).</t>
+          <t>Fondo violeta con las cuatro opciones como botones grandes.</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B17" s="42" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="C17" s="42" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B21" s="37" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="C21" s="37" t="inlineStr">
@@ -2289,40 +2289,40 @@
       </c>
       <c r="E21" s="39" t="inlineStr">
         <is>
-          <t>Dato / Beneficio</t>
+          <t>Producto / Función</t>
         </is>
       </c>
       <c r="F21" s="38" t="inlineStr">
         <is>
-          <t>Imagen</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="G21" s="40" t="inlineStr">
         <is>
-          <t>La trazabilidad es la que te salva en la auditoría</t>
+          <t>El hallazgo se escribe una sola vez</t>
         </is>
       </c>
       <c r="H21" s="38" t="inlineStr">
         <is>
-          <t>El auditor no solo mira QUÉ hiciste, sino que puedas DEMOSTRARLO: quién, cuándo y sobre qué versión. 🧾
-Control de versiones + registros con fecha y responsable = trazabilidad total.
-Cuando todo queda registrado solo (no a mano), la auditoría deja de ser una prueba de memoria.
-[Dato: sumá tu métrica de hallazgos evitados]</t>
+          <t>El auditor lo anota en el celular. Después alguien lo copia a la planilla de desvíos. Y después alguien lo vuelve a copiar al módulo de no conformidades.
+Tres veces el mismo texto, con tres oportunidades de que se pierda por el camino.
+Ahora el auditor lo califica una vez, en sitio: no conformidad mayor, menor, observación u oportunidad de mejora. Con eso la planilla de Hallazgos / Desvíos del informe se arma sola.
+Y solo los incumplimientos abren acción correctiva. Una oportunidad de mejora que dispara una CAPA te infla el tablero con cosas que no son un problema.</t>
         </is>
       </c>
       <c r="I21" s="38" t="inlineStr">
         <is>
-          <t>#ISO9001 #ISO14001 #ISO45001 #SistemasDeGestión #Calidad #Trazabilidad #Compliance #Auditorías</t>
+          <t>#AuditoríasEnLínea #SGI #ISO9001 #ISO45001 #AuditoríaInterna #Mendoza</t>
         </is>
       </c>
       <c r="J21" s="38" t="inlineStr">
         <is>
-          <t>Guardá este post para tu próxima auditoría 🔖</t>
+          <t>Mirá cómo queda el informe → auditoriasenlinea.com.ar</t>
         </is>
       </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
-          <t>Imagen: línea de tiempo de versiones de un documento.</t>
+          <t>Carrusel: slide 1 celular calificando el hallazgo / slide 2 las cuatro categorías con sus colores / slide 3 la planilla llenándose sola / slide 4 el informe PDF.</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="C23" s="42" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B24" s="42" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>01/11/2026</t>
         </is>
       </c>
       <c r="C24" s="42" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>02/11/2026</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -2651,24 +2651,24 @@
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>Checklists en papel = doble trabajo: primero se completa a mano, después alguien lo transcribe a la computadora. Y en el medio se pierden hojas. 📄➡️🗑️
-Con la app, el auditor de campo carga una sola vez, desde el celular, con foto y GPS. Sin transcripción, sin hojas perdidas, sin errores de tipeo.
-El dato nace digital.</t>
+          <t>El auditor sale con una carpeta, una lapicera y la dirección anotada en un papelito. Vuelve a la oficina y empieza el segundo trabajo: pasar todo en limpio.
+En el camino se pierden las fotos, se confunde qué respuesta era de qué punto, y nadie se acuerda si la visita fue a las 9 o a las 11.
+La asignación le llega al celular con el domicilio, el horario, a quién buscar al llegar y el alcance de la visita. Responde ahí, con foto y ubicación, aunque no haya señal. El dato nace digital y no se transcribe nunca.</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>#ISO9001 #ISO14001 #ISO45001 #SistemasDeGestión #Calidad #AppMóvil #Auditorías #Offline</t>
+          <t>#AuditoríasEnLínea #SGI #ISO9001 #ISO45001 #AuditoríaInterna #Mendoza</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>Pedí tu demo gratis 👉 auditoriasenlinea.com.ar</t>
+          <t>Probá la app de campo → auditoriasenlinea.com.ar</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr">
         <is>
-          <t>Imagen: checklist de papel vs app en el celular.</t>
+          <t>Split: carpeta con papeles arrugados / celular con la tarjeta de la visita y el botón del mapa.</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
@@ -2693,40 +2693,39 @@
       </c>
       <c r="E28" s="39" t="inlineStr">
         <is>
-          <t>Dato / Beneficio</t>
+          <t>Consultor / Partner</t>
         </is>
       </c>
       <c r="F28" s="38" t="inlineStr">
         <is>
-          <t>Imagen</t>
+          <t>Imagen + texto</t>
         </is>
       </c>
       <c r="G28" s="40" t="inlineStr">
         <is>
-          <t>Certificar también abre puertas comerciales</t>
+          <t>Un auditor solo, quince clientes</t>
         </is>
       </c>
       <c r="H28" s="38" t="inlineStr">
         <is>
-          <t>Un SGI no es solo cumplir: es un argumento de venta. 💼
-Cada vez más clientes y licitaciones piden proveedores certificados en calidad, ambiente y seguridad.
-Tener tu sistema ordenado y demostrable te habilita a competir donde antes no podías.
-[Dato: mencioná un sector o cliente que exige certificación]</t>
+          <t>No hace falta ser una consultora grande para trabajar como una.
+Tu cartera entera vive en tu cuenta: cargás los clientes, asignás las visitas a tu equipo y cada informe sale con el nombre de la empresa auditada, su domicilio y su referente.
+Sin servidores, sin una instalación por cliente y sin licencias por puesto. Lo abrís desde cualquier dispositivo, y en el celular se agrega como una app más.</t>
         </is>
       </c>
       <c r="I28" s="38" t="inlineStr">
         <is>
-          <t>#ISO9001 #ISO14001 #ISO45001 #SistemasDeGestión #Calidad #Certificación #Negocios #Pymes</t>
+          <t>#AuditoríasEnLínea #AuditorLíder #Consultoría #ISO9001 #AuditoríaInterna #Mendoza</t>
         </is>
       </c>
       <c r="J28" s="38" t="inlineStr">
         <is>
-          <t>Conocé la plataforma 👉 auditoriasenlinea.com.ar</t>
+          <t>Armá tu cartera → auditoriasenlinea.com.ar</t>
         </is>
       </c>
       <c r="K28" s="38" t="inlineStr">
         <is>
-          <t>Imagen: sello ISO como 'llave' a nuevos mercados.</t>
+          <t>Una persona sola en su escritorio, y al lado la lista de quince empresas auditadas con su actividad.</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2735,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
@@ -2794,7 +2793,7 @@
       </c>
       <c r="B30" s="42" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="C30" s="42" t="inlineStr">
@@ -2854,7 +2853,7 @@
       </c>
       <c r="B31" s="42" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>08/11/2026</t>
         </is>
       </c>
       <c r="C31" s="42" t="inlineStr">
@@ -2912,7 +2911,7 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -2972,7 +2971,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>10/11/2026</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
@@ -2997,33 +2996,30 @@
       </c>
       <c r="G33" s="30" t="inlineStr">
         <is>
-          <t>Todo lo que hace la plataforma, en un vistazo</t>
+          <t>Elegís con cuánta plataforma empezás</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
         <is>
-          <t>21 módulos, un solo flujo de mejora continua (Planificar → Hacer → Verificar → Actuar). ♻️
-📋 Diagnóstico, contexto, objetivos y procesos
-📁 Documentos, aprobaciones y evidencia
-🔍 Auditorías (incluida la app de campo), no conformidades y KPIs
-🤖 Auditor de IA, SST y mantenimiento
-Calidad, ambiente y seguridad, integrados de punta a punta.
-¿Lo vemos con tus datos en una demo?</t>
+          <t>Un mes mostrando qué hace Auditorías en Línea. Para cerrar, el mapa completo:
+▸ **Auditorías** — programa, plan con tu propio correlativo, checklist propio o ISO, app de campo sin señal, cartera de clientes, hallazgos e informe firmado.
+▸ **SGI Completo** — todo lo anterior más diagnóstico de brechas, contexto, objetivos y riesgos, procesos, gestión documental con aprobaciones, competencias, equipos calibrados, proveedores, KPIs, huella de carbono y revisión por la dirección.
+Veintiún módulos en total. Vas a ver los que elegiste, y ni uno más.</t>
         </is>
       </c>
       <c r="I33" s="28" t="inlineStr">
         <is>
-          <t>#ISO9001 #ISO14001 #ISO45001 #SistemasDeGestión #Calidad #SGI #ISO9001 #ISO14001 #ISO45001</t>
+          <t>#AuditoríasEnLínea #SGI #ISO9001 #ISO45001 #AuditoríaInterna #Mendoza</t>
         </is>
       </c>
       <c r="J33" s="28" t="inlineStr">
         <is>
-          <t>Pedí tu demo gratis 👉 auditoriasenlinea.com.ar</t>
+          <t>Creá tu cuenta gratis → auditoriasenlinea.com.ar</t>
         </is>
       </c>
       <c r="K33" s="28" t="inlineStr">
         <is>
-          <t>Carrusel resumen (o el brochure) con el mapa de módulos PDCA.</t>
+          <t>Carrusel: slide 1 las dos ediciones / slides 2-3 los módulos de cada una / slide 4 CTA con el logo.</t>
         </is>
       </c>
     </row>
